--- a/data/arrivals/Arrivals 11.2026/Arrivals 18.11.2026.XLSX
+++ b/data/arrivals/Arrivals 11.2026/Arrivals 18.11.2026.XLSX
@@ -1,17 +1,26 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10426"/>
+  <workbookPr defaultThemeVersion="202300"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jayeetra/Documents/GitHub/radisson_bristol/data/arrivals/Arrivals 11.2026/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{198EEB76-22A5-DF4D-8D80-F8CDC0778E47}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="21855" windowHeight="14940"/>
+    <workbookView xWindow="680" yWindow="680" windowWidth="27800" windowHeight="16960" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="137" uniqueCount="78">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="139" uniqueCount="78">
   <si>
     <t/>
   </si>
@@ -82,15 +91,14 @@
     <t>SEA - SEM EMEA</t>
   </si>
   <si>
-    <t> - Prepare check-in &amp; assign room (upgrade based on availability) 
-- Supply guest room with complimentary water
-</t>
-  </si>
-  <si>
-    <t> RR_CLUB</t>
-  </si>
-  <si>
-    <t> Rewards - CLUB</t>
+    <t>- Prepare check-in &amp; assign room (upgrade based on availability) 
+- Supply guest room with complimentary water</t>
+  </si>
+  <si>
+    <t>RR_CLUB</t>
+  </si>
+  <si>
+    <t>Rewards - CLUB</t>
   </si>
   <si>
     <t>Section</t>
@@ -114,13 +122,13 @@
     <t>Time</t>
   </si>
   <si>
-    <t>  AD</t>
-  </si>
-  <si>
-    <t>  CH</t>
-  </si>
-  <si>
-    <t>  IN</t>
+    <t>AD</t>
+  </si>
+  <si>
+    <t>CH</t>
+  </si>
+  <si>
+    <t>IN</t>
   </si>
   <si>
     <t>Tot. guests</t>
@@ -252,24 +260,22 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
-    <numFmt numFmtId="168" formatCode="[$-F400]h:mm:ss\ AM/PM"/>
-    <numFmt numFmtId="168" formatCode="[$-F400]h:mm:ss\ AM/PM"/>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="[$-F400]h:mm:ss\ AM/PM"/>
   </numFmts>
-  <fonts count="2">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
     </font>
     <font>
-      <u/>
       <sz val="10"/>
-      <color indexed="12"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -285,12 +291,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor indexed="13"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor indexed="43"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -319,14 +319,10 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="top"/>
-      <protection locked="0"/>
-    </xf>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
@@ -337,9 +333,9 @@
       <alignment horizontal="right" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment indent="2" vertical="top"/>
+      <alignment vertical="top" indent="2"/>
     </xf>
-    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top"/>
     </xf>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
@@ -351,30 +347,40 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="14" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top"/>
     </xf>
-    <xf numFmtId="168" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top"/>
     </xf>
-    <xf numFmtId="3" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1" vertical="top"/>
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
-<file path=xl/worksheets/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>4</xdr:col>
@@ -390,30 +396,36 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="Picture@QD\QApplication package@" descr="@QD\QApplication package@"/>
+        <xdr:cNvPr id="2" name="Picture@QD\QApplication package@" descr="@QD\QApplication package@">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvPicPr preferRelativeResize="0">
-          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeArrowheads="1"/>
+          <a:picLocks noChangeArrowheads="1"/>
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
-        <a:srcRect xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:srcRect/>
+        <a:stretch>
           <a:fillRect/>
         </a:stretch>
       </xdr:blipFill>
       <xdr:spPr bwMode="auto">
-        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:xfrm>
           <a:off x="5334000" y="161925"/>
           <a:ext cx="152400" cy="0"/>
         </a:xfrm>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
+        <a:prstGeom prst="rect">
           <a:avLst/>
         </a:prstGeom>
-        <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:solidFill>
           <a:srgbClr val="FFFFFF"/>
         </a:solidFill>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525">
+        <a:ln w="9525">
           <a:solidFill>
             <a:srgbClr val="000000"/>
           </a:solidFill>
@@ -427,67 +439,378 @@
 </xdr:wsDr>
 </file>
 
+<file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+  <a:themeElements>
+    <a:clrScheme name="Office">
+      <a:dk1>
+        <a:sysClr val="windowText" lastClr="000000"/>
+      </a:dk1>
+      <a:lt1>
+        <a:sysClr val="window" lastClr="FFFFFF"/>
+      </a:lt1>
+      <a:dk2>
+        <a:srgbClr val="0E2841"/>
+      </a:dk2>
+      <a:lt2>
+        <a:srgbClr val="E8E8E8"/>
+      </a:lt2>
+      <a:accent1>
+        <a:srgbClr val="156082"/>
+      </a:accent1>
+      <a:accent2>
+        <a:srgbClr val="E97132"/>
+      </a:accent2>
+      <a:accent3>
+        <a:srgbClr val="196B24"/>
+      </a:accent3>
+      <a:accent4>
+        <a:srgbClr val="0F9ED5"/>
+      </a:accent4>
+      <a:accent5>
+        <a:srgbClr val="A02B93"/>
+      </a:accent5>
+      <a:accent6>
+        <a:srgbClr val="4EA72E"/>
+      </a:accent6>
+      <a:hlink>
+        <a:srgbClr val="467886"/>
+      </a:hlink>
+      <a:folHlink>
+        <a:srgbClr val="96607D"/>
+      </a:folHlink>
+    </a:clrScheme>
+    <a:fontScheme name="Office">
+      <a:majorFont>
+        <a:latin typeface="Aptos Display" panose="02110004020202020204"/>
+        <a:ea typeface=""/>
+        <a:cs typeface=""/>
+        <a:font script="Jpan" typeface="游ゴシック Light"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="等线 Light"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Times New Roman"/>
+        <a:font script="Hebr" typeface="Times New Roman"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="MoolBoran"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Times New Roman"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
+      </a:majorFont>
+      <a:minorFont>
+        <a:latin typeface="Aptos Narrow" panose="02110004020202020204"/>
+        <a:ea typeface=""/>
+        <a:cs typeface=""/>
+        <a:font script="Jpan" typeface="游ゴシック"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="等线"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Arial"/>
+        <a:font script="Hebr" typeface="Arial"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="DaunPenh"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Arial"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
+      </a:minorFont>
+    </a:fontScheme>
+    <a:fmtScheme name="Office">
+      <a:fillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:lumMod val="110000"/>
+                <a:satMod val="105000"/>
+                <a:tint val="67000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="50000">
+              <a:schemeClr val="phClr">
+                <a:lumMod val="105000"/>
+                <a:satMod val="103000"/>
+                <a:tint val="73000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:lumMod val="105000"/>
+                <a:satMod val="109000"/>
+                <a:tint val="81000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="5400000" scaled="0"/>
+        </a:gradFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:satMod val="103000"/>
+                <a:lumMod val="102000"/>
+                <a:tint val="94000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="50000">
+              <a:schemeClr val="phClr">
+                <a:satMod val="110000"/>
+                <a:lumMod val="100000"/>
+                <a:shade val="100000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:lumMod val="99000"/>
+                <a:satMod val="120000"/>
+                <a:shade val="78000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="5400000" scaled="0"/>
+        </a:gradFill>
+      </a:fillStyleLst>
+      <a:lnStyleLst>
+        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+      </a:lnStyleLst>
+      <a:effectStyleLst>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst>
+            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="63000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+        </a:effectStyle>
+      </a:effectStyleLst>
+      <a:bgFillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr">
+            <a:tint val="95000"/>
+            <a:satMod val="170000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="93000"/>
+                <a:satMod val="150000"/>
+                <a:shade val="98000"/>
+                <a:lumMod val="102000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="50000">
+              <a:schemeClr val="phClr">
+                <a:tint val="98000"/>
+                <a:satMod val="130000"/>
+                <a:shade val="90000"/>
+                <a:lumMod val="103000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:shade val="63000"/>
+                <a:satMod val="120000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="5400000" scaled="0"/>
+        </a:gradFill>
+      </a:bgFillStyleLst>
+    </a:fmtScheme>
+  </a:themeElements>
+  <a:objectDefaults>
+    <a:lnDef>
+      <a:spPr/>
+      <a:bodyPr/>
+      <a:lstStyle/>
+      <a:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </a:style>
+    </a:lnDef>
+  </a:objectDefaults>
+  <a:extraClrSchemeLst/>
+  <a:extLst>
+    <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{2E142A2C-CD16-42D6-873A-C26D2A0506FA}" vid="{1BDDFF52-6CD6-40A5-AB3C-68EB2F1E4D0A}"/>
+    </a:ext>
+  </a:extLst>
+</a:theme>
+</file>
+
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:BA3"/>
-  <sheetFormatPr defaultRowHeight="12.75"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:BB3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="13" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" bestFit="1" width="9" customWidth="1"/>
-    <col min="2" max="2" bestFit="1" width="14" customWidth="1"/>
-    <col min="3" max="3" bestFit="1" width="8" customWidth="1"/>
-    <col min="4" max="4" bestFit="1" width="6" customWidth="1"/>
-    <col min="5" max="5" bestFit="1" width="14" customWidth="1"/>
-    <col min="6" max="6" bestFit="1" width="12" customWidth="1"/>
-    <col min="7" max="7" bestFit="1" width="13" customWidth="1"/>
-    <col min="8" max="8" bestFit="1" width="6" customWidth="1"/>
-    <col min="9" max="9" bestFit="1" width="3" customWidth="1"/>
-    <col min="10" max="10" bestFit="1" width="6" customWidth="1"/>
-    <col min="11" max="11" bestFit="1" width="6" customWidth="1"/>
-    <col min="12" max="12" bestFit="1" width="8" customWidth="1"/>
-    <col min="13" max="13" bestFit="1" width="17" customWidth="1"/>
-    <col min="14" max="14" bestFit="1" width="12" customWidth="1"/>
-    <col min="15" max="15" bestFit="1" width="10" customWidth="1"/>
-    <col min="16" max="16" bestFit="1" width="11" customWidth="1"/>
-    <col min="17" max="17" bestFit="1" width="14" customWidth="1"/>
-    <col min="18" max="18" bestFit="1" width="5" customWidth="1"/>
-    <col min="19" max="19" bestFit="1" width="16" customWidth="1"/>
-    <col min="20" max="20" bestFit="1" width="8" customWidth="1"/>
-    <col min="21" max="21" bestFit="1" width="12" customWidth="1"/>
-    <col min="22" max="22" bestFit="1" width="23" customWidth="1"/>
-    <col min="23" max="23" bestFit="1" width="12" customWidth="1"/>
-    <col min="24" max="24" bestFit="1" width="23" customWidth="1"/>
-    <col min="25" max="25" bestFit="1" width="8" customWidth="1"/>
-    <col min="26" max="26" bestFit="1" width="8" customWidth="1"/>
-    <col min="27" max="27" bestFit="1" width="13" customWidth="1"/>
-    <col min="28" max="28" bestFit="1" width="11" customWidth="1"/>
-    <col min="29" max="29" bestFit="1" width="11" customWidth="1"/>
-    <col min="30" max="30" bestFit="1" width="16" customWidth="1"/>
-    <col min="31" max="31" bestFit="1" width="8" customWidth="1"/>
-    <col min="32" max="32" bestFit="1" width="23" customWidth="1"/>
-    <col min="33" max="33" bestFit="1" width="15" customWidth="1"/>
-    <col min="34" max="34" bestFit="1" width="12" customWidth="1"/>
-    <col min="35" max="35" bestFit="1" width="13" customWidth="1"/>
-    <col min="36" max="36" bestFit="1" width="11" customWidth="1"/>
-    <col min="37" max="37" bestFit="1" width="13" customWidth="1"/>
-    <col min="38" max="38" bestFit="1" width="24" customWidth="1"/>
-    <col min="39" max="39" bestFit="1" width="16" customWidth="1"/>
-    <col min="40" max="40" bestFit="1" width="22" customWidth="1"/>
-    <col min="41" max="41" bestFit="1" width="20" customWidth="1"/>
-    <col min="42" max="42" bestFit="1" width="14" customWidth="1"/>
-    <col min="43" max="43" bestFit="1" width="15" customWidth="1"/>
-    <col min="44" max="44" bestFit="1" width="10" customWidth="1"/>
-    <col min="45" max="45" bestFit="1" width="13" customWidth="1"/>
-    <col min="46" max="46" bestFit="1" width="20" customWidth="1"/>
-    <col min="47" max="47" bestFit="1" width="118" customWidth="1"/>
-    <col min="48" max="48" bestFit="1" width="24" customWidth="1"/>
-    <col min="49" max="49" bestFit="1" width="6" customWidth="1"/>
-    <col min="50" max="50" bestFit="1" width="6" customWidth="1"/>
-    <col min="51" max="51" bestFit="1" width="16" customWidth="1"/>
-    <col min="52" max="52" bestFit="1" width="25" customWidth="1"/>
-    <col min="53" max="53" bestFit="1" width="10" customWidth="1"/>
+    <col min="1" max="1" width="9" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="8" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="6" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="6" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="3" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="6" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="8" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="17" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="12" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="10" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="11" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="5" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="16" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="8" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="12" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="23" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="12" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="23" bestFit="1" customWidth="1"/>
+    <col min="25" max="26" width="8" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="13" bestFit="1" customWidth="1"/>
+    <col min="28" max="29" width="11" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="16" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="8" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="23" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="15" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="12" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="13" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="11" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="13" bestFit="1" customWidth="1"/>
+    <col min="38" max="38" width="24" bestFit="1" customWidth="1"/>
+    <col min="39" max="39" width="16" bestFit="1" customWidth="1"/>
+    <col min="40" max="40" width="22" bestFit="1" customWidth="1"/>
+    <col min="41" max="41" width="20" bestFit="1" customWidth="1"/>
+    <col min="42" max="42" width="14" bestFit="1" customWidth="1"/>
+    <col min="43" max="43" width="15" bestFit="1" customWidth="1"/>
+    <col min="44" max="44" width="10" bestFit="1" customWidth="1"/>
+    <col min="45" max="45" width="13" bestFit="1" customWidth="1"/>
+    <col min="46" max="46" width="20" bestFit="1" customWidth="1"/>
+    <col min="47" max="47" width="118" bestFit="1" customWidth="1"/>
+    <col min="48" max="48" width="24" bestFit="1" customWidth="1"/>
+    <col min="49" max="50" width="6" bestFit="1" customWidth="1"/>
+    <col min="51" max="51" width="16" bestFit="1" customWidth="1"/>
+    <col min="52" max="52" width="25" bestFit="1" customWidth="1"/>
+    <col min="53" max="53" width="10" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:53">
+    <row r="1" spans="1:54" ht="42" x14ac:dyDescent="0.15">
       <c r="A1" s="1" t="s">
         <v>26</v>
       </c>
@@ -647,8 +970,11 @@
       <c r="BA1" s="1" t="s">
         <v>77</v>
       </c>
+      <c r="BB1" s="12" t="s">
+        <v>53</v>
+      </c>
     </row>
-    <row r="2" spans="1:53" ht="14" customHeight="1">
+    <row r="2" spans="1:54" ht="14" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A2" t="s">
         <v>0</v>
       </c>
@@ -668,7 +994,7 @@
         <v>2</v>
       </c>
       <c r="G2" s="4">
-        <v>0 </v>
+        <v>0</v>
       </c>
       <c r="H2" s="5">
         <v>2</v>
@@ -794,7 +1120,7 @@
         <v>0</v>
       </c>
       <c r="AW2" s="6">
-        <v>0.00</v>
+        <v>0</v>
       </c>
       <c r="AX2" t="s">
         <v>0</v>
@@ -808,8 +1134,11 @@
       <c r="BA2" t="s">
         <v>0</v>
       </c>
+      <c r="BB2">
+        <v>50</v>
+      </c>
     </row>
-    <row r="3" spans="1:53">
+    <row r="3" spans="1:54" x14ac:dyDescent="0.15">
       <c r="A3" s="7" t="s">
         <v>0</v>
       </c>
@@ -957,6 +1286,9 @@
         <v>0</v>
       </c>
       <c r="BA3" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="BB3" s="7" t="s">
         <v>0</v>
       </c>
     </row>
@@ -964,6 +1296,6 @@
   <phoneticPr fontId="0" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter alignWithMargins="0"/>
-  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>